--- a/lp_list.xlsx
+++ b/lp_list.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C420"/>
+  <dimension ref="A1:C421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6724,6 +6724,21 @@
         </is>
       </c>
     </row>
+    <row r="421">
+      <c r="A421" t="n">
+        <v>496</v>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Milli Vanili (밀리 바닐리)</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Baby Don't Forget My Number</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lp_list.xlsx
+++ b/lp_list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LP_Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{302FA74D-C215-4F6F-B4FA-458553BBE0CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536AA7A8-578C-486B-8ABC-4561E1A05AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2089,7 +2089,8 @@
     <t>Milli Vanili (밀리 바닐리)</t>
   </si>
   <si>
-    <t>Baby Don't Forget My Number</t>
+    <t>Baby Don't Forget My Number /45rpm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
